--- a/Whizzard_Downloads/Daily_Open_Ticket_Reports/Current_Month_Open_Tickets_16-10-26.xlsx
+++ b/Whizzard_Downloads/Daily_Open_Ticket_Reports/Current_Month_Open_Tickets_16-10-26.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16 Oct 2026 01:13 PM</t>
+          <t>16 Oct 2026 07:44 AM</t>
         </is>
       </c>
     </row>

--- a/Whizzard_Downloads/Daily_Open_Ticket_Reports/Current_Month_Open_Tickets_16-10-26.xlsx
+++ b/Whizzard_Downloads/Daily_Open_Ticket_Reports/Current_Month_Open_Tickets_16-10-26.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16 Oct 2026 07:44 AM</t>
+          <t>16 Oct 2026 08:03 AM</t>
         </is>
       </c>
     </row>

--- a/Whizzard_Downloads/Daily_Open_Ticket_Reports/Current_Month_Open_Tickets_16-10-26.xlsx
+++ b/Whizzard_Downloads/Daily_Open_Ticket_Reports/Current_Month_Open_Tickets_16-10-26.xlsx
@@ -14,9 +14,9 @@
     <sheet name="All Current Month" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Completed Tickets'!$A$1:$N$83</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Completed Today'!$A$1:$N$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Open Tickets'!$A$1:$N$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Completed Tickets'!$A$1:$N$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Completed Today'!$A$1:$N$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Open Tickets'!$A$1:$N$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'All Current Month'!$A$1:$AI$120</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -191,8 +191,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CompletedTicketsTable" displayName="CompletedTicketsTable" ref="A1:N83" headerRowCount="1">
-  <autoFilter ref="A1:N83"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CompletedTicketsTable" displayName="CompletedTicketsTable" ref="A1:N84" headerRowCount="1">
+  <autoFilter ref="A1:N84"/>
   <tableColumns count="14">
     <tableColumn id="1" name="Ticket Source"/>
     <tableColumn id="2" name="Ticket ID"/>
@@ -214,8 +214,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTodayTable" displayName="CompletedTodayTable" ref="A1:N4" headerRowCount="1">
-  <autoFilter ref="A1:N4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CompletedTodayTable" displayName="CompletedTodayTable" ref="A1:N5" headerRowCount="1">
+  <autoFilter ref="A1:N5"/>
   <tableColumns count="14">
     <tableColumn id="1" name="Ticket Source"/>
     <tableColumn id="2" name="Ticket ID"/>
@@ -237,8 +237,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="OpenTicketsTable" displayName="OpenTicketsTable" ref="A1:N31" headerRowCount="1">
-  <autoFilter ref="A1:N31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="OpenTicketsTable" displayName="OpenTicketsTable" ref="A1:N30" headerRowCount="1">
+  <autoFilter ref="A1:N30"/>
   <tableColumns count="14">
     <tableColumn id="1" name="Ticket Source"/>
     <tableColumn id="2" name="Ticket ID"/>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -628,7 +628,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -683,7 +683,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16 Oct 2026 08:03 AM</t>
+          <t>16 Oct 2026 09:15 AM</t>
         </is>
       </c>
     </row>
@@ -775,13 +775,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
         <v>21</v>
@@ -847,13 +847,13 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>119</v>
@@ -884,7 +884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N83"/>
+  <dimension ref="A1:N84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2610070</t>
+          <t>2610081</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4053,18 +4053,18 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>13 Oct 2026</t>
+          <t>16 Oct 2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Balerao Ramesh</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>TS09UD7747</t>
+          <t>TS09UD7736</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4085,7 +4085,7 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Vehicle battery down</t>
+          <t>VEHICLE NOT MOVING</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2610068</t>
+          <t>2610070</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4128,12 +4128,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>TS09UD7744</t>
+          <t>TS09UD7747</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>HYDM</t>
+          <t>HYBH</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4149,12 +4149,12 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Vehicle Breakdown Due to Tyre Issue</t>
+          <t>Vehicle battery down</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Mulukuri Uha</t>
+          <t>Syed Rameez</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4171,54 +4171,54 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2610045</t>
+          <t>2610068</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>08 Oct 2026</t>
+          <t>16 Oct 2026</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>08 Oct 2026</t>
+          <t>13 Oct 2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Debanjan Sarkar</t>
+          <t>System</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>MH47AW0520</t>
+          <t>TS09UD7744</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>KKFG01</t>
+          <t>HYDM</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Debanjan Sarkar</t>
+          <t>Balerao Ramesh</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>BREAKDOWN</t>
+          <t>Vehicle Breakdown Due to Tyre Issue</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Anupam Das</t>
+          <t>Mulukuri Uha</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2610039</t>
+          <t>2610045</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>12 Oct 2026</t>
+          <t>08 Oct 2026</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4251,38 +4251,38 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Balerao Ramesh</t>
+          <t>Debanjan Sarkar</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>TS09UD7802</t>
+          <t>MH47AW0520</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>HYDM</t>
+          <t>KKFG01</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Balerao Ramesh</t>
+          <t>Debanjan Sarkar</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>vehicle brakes are not working</t>
+          <t>BREAKDOWN</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Mulukuri Uha</t>
+          <t>Anupam Das</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4299,54 +4299,54 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2610037</t>
+          <t>2610039</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
+          <t>12 Oct 2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
           <t>08 Oct 2026</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>07 Oct 2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Munnindra Kumar</t>
+          <t>Balerao Ramesh</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>DL51GD1629</t>
+          <t>TS09UD7802</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>DEFE06</t>
+          <t>HYDM</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Munnindra Kumar</t>
+          <t>Balerao Ramesh</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>EV not working</t>
+          <t>vehicle brakes are not working</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Shubham Singh</t>
+          <t>Mulukuri Uha</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2610036</t>
+          <t>2610037</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>DL51GD8770</t>
+          <t>DL51GD1629</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4427,54 +4427,54 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2610034</t>
+          <t>2610036</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>12 Oct 2026</t>
+          <t>08 Oct 2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>06 Oct 2026</t>
+          <t>07 Oct 2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Balerao Ramesh</t>
+          <t>Munnindra Kumar</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>TS09UD7127</t>
+          <t>DL51GD8770</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>HYBV</t>
+          <t>DEFE06</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Balerao Ramesh</t>
+          <t>Munnindra Kumar</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Breakdown at Hub</t>
+          <t>EV not working</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Santosh . S</t>
+          <t>Shubham Singh</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4491,33 +4491,33 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2610033</t>
+          <t>2610034</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>08 Oct 2026</t>
+          <t>12 Oct 2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>05 Oct 2026</t>
+          <t>06 Oct 2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Balerao Ramesh</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>TS09UD7736</t>
+          <t>TS09UD7127</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>HYDM</t>
+          <t>HYBV</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4533,12 +4533,12 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>D-Mart is currently not accepting this vehicle due to frequent breakdowns</t>
+          <t>Breakdown at Hub</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Mulukuri Uha</t>
+          <t>Santosh . S</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2610032</t>
+          <t>2610033</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>12 Oct 2026</t>
+          <t>08 Oct 2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4571,12 +4571,12 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Balerao Ramesh</t>
+          <t>System</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>TS09UD6501</t>
+          <t>TS09UD7736</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4597,7 +4597,7 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Vehicle not operational due to a charging issue.</t>
+          <t>D-Mart is currently not accepting this vehicle due to frequent breakdowns</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2610031</t>
+          <t>2610032</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>06 Oct 2026</t>
+          <t>12 Oct 2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4635,22 +4635,22 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Debanjan Sarkar</t>
+          <t>Balerao Ramesh</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>WB25L3238</t>
+          <t>TS09UD6501</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>ASFG01</t>
+          <t>HYDM</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Debanjan Sarkar</t>
+          <t>Balerao Ramesh</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4661,12 +4661,12 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>BREAKDOWN</t>
+          <t>Vehicle not operational due to a charging issue.</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Anupam Das</t>
+          <t>Mulukuri Uha</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4683,38 +4683,38 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2610015</t>
+          <t>2610031</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>12 Oct 2026</t>
+          <t>06 Oct 2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>02 Oct 2026</t>
+          <t>05 Oct 2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Balerao Ramesh</t>
+          <t>Debanjan Sarkar</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>TS09UD7739</t>
+          <t>WB25L3238</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>HYBZ</t>
+          <t>ASFG01</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Balerao Ramesh</t>
+          <t>Debanjan Sarkar</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4725,12 +4725,12 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Not Moveing</t>
+          <t>BREAKDOWN</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Sridhar Mekala</t>
+          <t>Anupam Das</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4747,38 +4747,38 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2610010</t>
+          <t>2610015</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>03 Oct 2026</t>
+          <t>12 Oct 2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>01 Oct 2026</t>
+          <t>02 Oct 2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Debanjan Sarkar</t>
+          <t>Balerao Ramesh</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>WB19L7244</t>
+          <t>TS09UD7739</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>KKFG09</t>
+          <t>HYBZ</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Debanjan Sarkar</t>
+          <t>Balerao Ramesh</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4789,12 +4789,12 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>BREAKDOWN</t>
+          <t>Not Moveing</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Anupam Das</t>
+          <t>Sridhar Mekala</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2610005</t>
+          <t>2610010</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>09 Oct 2026</t>
+          <t>03 Oct 2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4827,38 +4827,38 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Debanjan Sarkar</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>KA04AD1752</t>
+          <t>WB19L7244</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>BADE01</t>
+          <t>KKFG09</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>S Kalleshappa</t>
+          <t>Debanjan Sarkar</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>moved to SC</t>
+          <t>BREAKDOWN</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>P.S Ekadanta</t>
+          <t>Anupam Das</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2610004</t>
+          <t>2610005</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>KA04AC8861</t>
+          <t>KA04AD1752</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>BADE02</t>
+          <t>BADE01</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2610003</t>
+          <t>2610004</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>01 Oct 2026</t>
+          <t>09 Oct 2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4955,22 +4955,22 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Balerao Ramesh</t>
+          <t>System</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>TS09UD6501</t>
+          <t>KA04AC8861</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>HYDM</t>
+          <t>BADE02</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Balerao Ramesh</t>
+          <t>S Kalleshappa</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4981,12 +4981,12 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>The auxiliary battery issue has not been resolved yet.</t>
+          <t>moved to SC</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Mulukuri Uha</t>
+          <t>P.S Ekadanta</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4998,30 +4998,38 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Vehicle Requisition</t>
+          <t>Service Request</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>VRQ-2610029</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>2610003</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>01 Oct 2026</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>14/10/2026</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
+          <t>01 Oct 2026</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Balerao Ramesh</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>TS09UD6501</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>HYBH</t>
+          <t>HYDM</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5034,20 +5042,20 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>The auxiliary battery issue has not been resolved yet.</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Syed Rameez</t>
+          <t>Mulukuri Uha</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Vehicle_Requisition_2026-10.csv</t>
+          <t>Service_Request_2026-10.csv</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5067,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VRQ-2610028</t>
+          <t>VRQ-2610029</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -5070,19 +5078,19 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>15/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>DEFE06</t>
+          <t>HYBH</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Munnindra Kumar</t>
+          <t>Balerao Ramesh</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -5092,13 +5100,13 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Shubham Singh</t>
+          <t>Syed Rameez</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -5115,7 +5123,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>VRQ-2610027</t>
+          <t>VRQ-2610028</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -5171,7 +5179,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VRQ-2610026</t>
+          <t>VRQ-2610027</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -5227,30 +5235,30 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>VRQ-2610025</t>
+          <t>VRQ-2610026</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>15/10/2026</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>HYDM</t>
+          <t>DEFE06</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Balerao Ramesh</t>
+          <t>Munnindra Kumar</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -5260,13 +5268,13 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Mulukuri Uha</t>
+          <t>Shubham Singh</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5283,25 +5291,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>VRQ-2610024</t>
+          <t>VRQ-2610025</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>HYBH</t>
+          <t>HYDM</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5316,13 +5324,13 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Syed Rameez</t>
+          <t>Mulukuri Uha</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5339,7 +5347,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VRQ-2610023</t>
+          <t>VRQ-2610024</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -5350,7 +5358,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -5372,7 +5380,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
@@ -5395,7 +5403,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>VRQ-2610022</t>
+          <t>VRQ-2610023</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -5451,30 +5459,30 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>VRQ-2610021</t>
+          <t>VRQ-2610022</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>10/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>HBDE</t>
+          <t>HYBH</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Rakesh Singh</t>
+          <t>Balerao Ramesh</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -5484,13 +5492,13 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Prashant Kumar</t>
+          <t>Syed Rameez</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5507,7 +5515,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>VRQ-2610020</t>
+          <t>VRQ-2610021</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -5563,7 +5571,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>VRQ-2610019</t>
+          <t>VRQ-2610020</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -5619,30 +5627,30 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>VRQ-2610018</t>
+          <t>VRQ-2610019</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>09/10/2026</t>
+          <t>10/10/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>HYDM</t>
+          <t>HBDE</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Balerao Ramesh</t>
+          <t>Rakesh Singh</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5652,13 +5660,13 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Mulukuri Uha</t>
+          <t>Prashant Kumar</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5675,13 +5683,13 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>VRQ-2610017</t>
+          <t>VRQ-2610018</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>09/10/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5693,12 +5701,12 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>KKFG09</t>
+          <t>HYDM</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Debanjan Sarkar</t>
+          <t>Balerao Ramesh</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5708,13 +5716,13 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Anupam Das</t>
+          <t>Mulukuri Uha</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5731,7 +5739,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>VRQ-2610016</t>
+          <t>VRQ-2610017</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -5742,7 +5750,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -5764,7 +5772,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -5787,7 +5795,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>VRQ-2610015</t>
+          <t>VRQ-2610016</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -5805,7 +5813,7 @@
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>HOFG01</t>
+          <t>KKFG09</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5843,7 +5851,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>VRQ-2610014</t>
+          <t>VRQ-2610015</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -5854,19 +5862,19 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>HBDE</t>
+          <t>HOFG01</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Rakesh Singh</t>
+          <t>Debanjan Sarkar</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5876,13 +5884,13 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Prashant Kumar</t>
+          <t>Anupam Das</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5899,30 +5907,30 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>VRQ-2610013</t>
+          <t>VRQ-2610014</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>13/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>HYBH</t>
+          <t>HBDE</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Balerao Ramesh</t>
+          <t>Rakesh Singh</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5932,13 +5940,13 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Syed Rameez</t>
+          <t>Prashant Kumar</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5955,7 +5963,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>VRQ-2610012</t>
+          <t>VRQ-2610013</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -5966,7 +5974,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>11/10/2026</t>
+          <t>13/10/2026</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
@@ -5988,7 +5996,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -6011,7 +6019,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>VRQ-2610011</t>
+          <t>VRQ-2610012</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -6067,7 +6075,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>VRQ-2610005</t>
+          <t>VRQ-2610011</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -6078,14 +6086,14 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>12/10/2026</t>
+          <t>11/10/2026</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>HYBZ</t>
+          <t>HYBH</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -6100,13 +6108,13 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Sridhar Mekala</t>
+          <t>Syed Rameez</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6123,7 +6131,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>VRQ-2610004</t>
+          <t>VRQ-2610005</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -6134,19 +6142,19 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>12/10/2026</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>GURP</t>
+          <t>HYBZ</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Rakesh Singh</t>
+          <t>Balerao Ramesh</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -6156,13 +6164,13 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Anubhav Panday</t>
+          <t>Sridhar Mekala</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6179,30 +6187,30 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>VRQ-2610001</t>
+          <t>VRQ-2610004</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>01/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>06/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>KKFG09</t>
+          <t>GURP</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Debanjan Sarkar</t>
+          <t>Rakesh Singh</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -6212,23 +6220,79 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
+          <t>Anubhav Panday</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Vehicle_Requisition_2026-10.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Vehicle Requisition</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>VRQ-2610001</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>KKFG09</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Debanjan Sarkar</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
           <t>Anupam Das</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t>Vehicle_Requisition_2026-10.csv</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N83"/>
+  <autoFilter ref="A1:N84"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6242,7 +6306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -6250,7 +6314,7 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
@@ -6409,7 +6473,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2610070</t>
+          <t>2610081</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -6419,18 +6483,18 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13 Oct 2026</t>
+          <t>16 Oct 2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Balerao Ramesh</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>TS09UD7747</t>
+          <t>TS09UD7736</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6451,7 +6515,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Vehicle battery down</t>
+          <t>VEHICLE NOT MOVING</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -6473,7 +6537,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2610068</t>
+          <t>2610070</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6494,12 +6558,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>TS09UD7744</t>
+          <t>TS09UD7747</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>HYDM</t>
+          <t>HYBH</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -6515,22 +6579,86 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
+          <t>Vehicle battery down</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Syed Rameez</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Service_Request_2026-10.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Service Request</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2610068</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>16 Oct 2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>13 Oct 2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TS09UD7744</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>HYDM</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Balerao Ramesh</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>Vehicle Breakdown Due to Tyre Issue</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Mulukuri Uha</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Service_Request_2026-10.csv</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N4"/>
+  <autoFilter ref="A1:N5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -6544,7 +6672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -7024,7 +7152,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>10 days</t>
+          <t>11 days</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -7092,7 +7220,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>10 days</t>
+          <t>11 days</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -7160,7 +7288,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>10 days</t>
+          <t>11 days</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -7228,7 +7356,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>10 days</t>
+          <t>11 days</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -7296,7 +7424,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>10 days</t>
+          <t>11 days</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -7364,7 +7492,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>10 days</t>
+          <t>11 days</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -7432,7 +7560,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>10 days</t>
+          <t>11 days</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -7500,7 +7628,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>10 days</t>
+          <t>11 days</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -7568,7 +7696,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>10 days</t>
+          <t>11 days</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -7636,7 +7764,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>10 days</t>
+          <t>11 days</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -7787,30 +7915,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2610081</t>
+          <t>2610079</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>16 Oct 2026</t>
+          <t>14 Oct 2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>TS09UD7736</t>
+          <t>MH02FL2348</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>HYBH</t>
+          <t>ISKO</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Balerao Ramesh</t>
+          <t>Ninad Nandkishor Sawant</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -7821,12 +7949,12 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>VEHICLE NOT MOVING</t>
+          <t>Breakdown</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Syed Rameez</t>
+          <t>Sandip Kedarnath Salpure</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -7843,7 +7971,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2610079</t>
+          <t>2610078</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -7856,7 +7984,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>MH02FL2348</t>
+          <t>TS09UD7791</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -7899,7 +8027,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2610078</t>
+          <t>2610077</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -7912,12 +8040,12 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>TS09UD7791</t>
+          <t>MH02GH5979</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>ISKO</t>
+          <t>NAFH01</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -7933,7 +8061,7 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Breakdown</t>
+          <t>Charger issue</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -7955,7 +8083,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2610077</t>
+          <t>2610076</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -7968,17 +8096,17 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>MH02GH5979</t>
+          <t>DL51GD1658</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>NAFH01</t>
+          <t>DEFE06</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Ninad Nandkishor Sawant</t>
+          <t>Shubham Singh</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -7989,12 +8117,12 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Charger issue</t>
+          <t>BREAK DOWN</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Sandip Kedarnath Salpure</t>
+          <t>Munnindra Kumar</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -8006,35 +8134,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Service Request</t>
+          <t>Vehicle Requisition</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2610076</t>
+          <t>VRQ-2610030</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>14 Oct 2026</t>
+          <t>14/10/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>DL51GD1658</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>DEFE06</t>
+          <t>HYBH</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Shubham Singh</t>
+          <t>Balerao Ramesh</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -8042,20 +8166,20 @@
           <t>Open</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>BREAK DOWN</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Munnindra Kumar</t>
+          <t>Syed Rameez</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Service_Request_2026-10.csv</t>
+          <t>Vehicle_Requisition_2026-10.csv</t>
         </is>
       </c>
     </row>
@@ -8067,13 +8191,13 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>VRQ-2610030</t>
+          <t>VRQ-2610010</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>07/10/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -8081,7 +8205,7 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>HYBH</t>
+          <t>HYBE</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -8096,13 +8220,13 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Syed Rameez</t>
+          <t>Sridhar Mekala</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -8119,7 +8243,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>VRQ-2610010</t>
+          <t>VRQ-2610009</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -8133,7 +8257,7 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>HYBE</t>
+          <t>HYBZ</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -8171,7 +8295,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>VRQ-2610009</t>
+          <t>VRQ-2610008</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -8223,7 +8347,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>VRQ-2610008</t>
+          <t>VRQ-2610007</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -8275,7 +8399,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VRQ-2610007</t>
+          <t>VRQ-2610006</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -8327,13 +8451,13 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VRQ-2610006</t>
+          <t>VRQ-2610003</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>07/10/2026</t>
+          <t>05/10/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -8341,12 +8465,12 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>HYBZ</t>
+          <t>KLHS</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Balerao Ramesh</t>
+          <t>Ninad Nandkishor Sawant</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -8356,13 +8480,13 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Sridhar Mekala</t>
+          <t>Sandip Kedarnath Salpure</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -8379,7 +8503,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>VRQ-2610003</t>
+          <t>VRQ-2610002</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -8393,7 +8517,7 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>KLHS</t>
+          <t>ISKO</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -8423,60 +8547,8 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Vehicle Requisition</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>VRQ-2610002</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>05/10/2026</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>ISKO</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Ninad Nandkishor Sawant</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Sandip Kedarnath Salpure</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Vehicle_Requisition_2026-10.csv</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:N31"/>
+  <autoFilter ref="A1:N30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -10098,7 +10170,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>10 days</t>
+          <t>11 days</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -10207,7 +10279,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>10 days</t>
+          <t>11 days</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -10316,7 +10388,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>10 days</t>
+          <t>11 days</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
@@ -10425,7 +10497,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>10 days</t>
+          <t>11 days</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
@@ -10534,7 +10606,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>10 days</t>
+          <t>11 days</t>
         </is>
       </c>
       <c r="R18" t="inlineStr"/>
@@ -10643,7 +10715,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>10 days</t>
+          <t>11 days</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
@@ -10752,7 +10824,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>10 days</t>
+          <t>11 days</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
@@ -10861,7 +10933,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>10 days</t>
+          <t>11 days</t>
         </is>
       </c>
       <c r="R21" t="inlineStr"/>
@@ -10970,7 +11042,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>10 days</t>
+          <t>11 days</t>
         </is>
       </c>
       <c r="R22" t="inlineStr"/>
@@ -11079,7 +11151,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>10 days</t>
+          <t>11 days</t>
         </is>
       </c>
       <c r="R23" t="inlineStr"/>
@@ -15376,7 +15448,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Accepted</t>
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
@@ -15389,12 +15461,12 @@
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Balerao Ramesh</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>16 Oct 2026</t>
         </is>
       </c>
       <c r="T64" t="inlineStr"/>
